--- a/CryoGrid/CryoGridCommunity_results/templates/automatic_loops/RESTART.xlsx
+++ b/CryoGrid/CryoGridCommunity_results/templates/automatic_loops/RESTART.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Utilisateurs\pozsgayv\Documents\CryoGrid_VP_Workflow\CryoGrid\CryoGridCommunity_results\templates\automatic_loops\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81B315DF-4ABB-4FF2-8B77-F24F5153C9F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8854239-FFBB-4960-BA41-EC552E46B877}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -715,9 +715,6 @@
       <c r="A18" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B18" s="5">
-        <v>2844</v>
-      </c>
       <c r="D18" s="1" t="s">
         <v>37</v>
       </c>
@@ -725,9 +722,6 @@
     <row r="19" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A19" s="5" t="s">
         <v>14</v>
-      </c>
-      <c r="B19" s="5">
-        <v>2790</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>38</v>
